--- a/photography_forms/023_photography_permit_registration_form--photography_forms.xlsx
+++ b/photography_forms/023_photography_permit_registration_form--photography_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>one_hour</t>
+          <t>two_hours</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>One hour</t>
+          <t>Two hours</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>two_hours</t>
+          <t>three_hours</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Two hours</t>
+          <t>Three hours</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>three_hours</t>
+          <t>four_hours</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Three hours</t>
+          <t>Four hours</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>four_hours</t>
+          <t>five_hours</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Four hours</t>
+          <t>Five hours</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>five_hours</t>
+          <t>full_day</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Five hours</t>
+          <t>Full day</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>full_day</t>
+          <t>multiple_days</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Full day</t>
+          <t>Multiple days</t>
         </is>
       </c>
     </row>
@@ -2355,29 +2355,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>multiple_days</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Multiple days</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>photo_permit_duration_choices</t>
+          <t>photo_permit_status_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -2406,29 +2406,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>photo_permit_status_choices</t>
+          <t>assigned_to_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2440,29 +2440,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_by_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2474,29 +2474,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>assigned_by_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2508,27 +2508,10 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>submitted_by_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
